--- a/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/TN WP 2026-27/SL 2.0/Dindigul.xlsx
+++ b/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/TN WP 2026-27/SL 2.0/Dindigul.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\TN\TN_2026-27\02 Sample List - TN 2026-27\2.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\TN\TN_2026-27\02 Sample List - TN 2026-27\SL 2.0 - v3 - revised - Incremental\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F6B96AE-752C-4FDA-A6A7-860B9C522C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B7911E-48D9-4F89-ADF6-03014857EBF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="140">
   <si>
     <t>State Sample</t>
   </si>
@@ -235,9 +235,6 @@
     <t>2</t>
   </si>
   <si>
-    <t>Total = 92</t>
-  </si>
-  <si>
     <t>Vedasandur</t>
   </si>
   <si>
@@ -439,6 +436,9 @@
     <t>Kallimanthavam</t>
   </si>
   <si>
+    <t>32</t>
+  </si>
+  <si>
     <t>Dindigul ( 13 )</t>
   </si>
   <si>
@@ -448,10 +448,7 @@
     <t>3/3,1</t>
   </si>
   <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>28</t>
+    <t>14</t>
   </si>
 </sst>
 </file>
@@ -779,9 +776,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -790,7 +784,46 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -804,50 +837,14 @@
     <xf numFmtId="49" fontId="5" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1182,106 +1179,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="47"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="46"/>
     </row>
     <row r="2" spans="1:12" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="47"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="46"/>
     </row>
     <row r="3" spans="1:12" s="6" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="47" t="s">
         <v>136</v>
       </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48" t="s">
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="49"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="48"/>
     </row>
     <row r="4" spans="1:12" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
+      <c r="A4" s="49"/>
+      <c r="B4" s="49"/>
       <c r="C4" s="50"/>
       <c r="D4" s="50"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48" t="s">
+      <c r="E4" s="49"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="48"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="66" t="s">
+      <c r="H4" s="47"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="58" t="s">
         <v>137</v>
       </c>
-      <c r="K4" s="66"/>
-      <c r="L4" s="66"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="67" t="s">
+      <c r="B5" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="63" t="s">
+      <c r="C5" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="64"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="60" t="s">
+      <c r="D5" s="56"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60" t="s">
+      <c r="G5" s="52"/>
+      <c r="H5" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60" t="s">
+      <c r="I5" s="52"/>
+      <c r="J5" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="K5" s="60"/>
-      <c r="L5" s="60" t="s">
+      <c r="K5" s="52"/>
+      <c r="L5" s="52" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="62"/>
-      <c r="B6" s="68"/>
+      <c r="A6" s="54"/>
+      <c r="B6" s="60"/>
       <c r="C6" s="7" t="s">
         <v>7</v>
       </c>
@@ -1309,7 +1306,7 @@
       <c r="K6" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="L6" s="60"/>
+      <c r="L6" s="52"/>
     </row>
     <row r="7" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
@@ -1533,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="41" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L12" s="4">
         <v>6</v>
@@ -1568,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="41" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K13" s="5">
         <v>0</v>
@@ -1606,7 +1603,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K14" s="5">
         <v>0</v>
@@ -1644,7 +1641,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K15" s="5">
         <v>0</v>
@@ -1820,10 +1817,8 @@
       <c r="L20" s="45"/>
     </row>
     <row r="21" spans="1:12" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J21" s="59" t="s">
-        <v>68</v>
-      </c>
-      <c r="K21" s="59"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -3372,144 +3367,144 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
-      <c r="S1" s="57"/>
-      <c r="T1" s="57"/>
-      <c r="U1" s="57"/>
-      <c r="V1" s="57"/>
-      <c r="W1" s="57"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="61"/>
+      <c r="P1" s="61"/>
+      <c r="Q1" s="61"/>
+      <c r="R1" s="61"/>
+      <c r="S1" s="61"/>
+      <c r="T1" s="61"/>
+      <c r="U1" s="61"/>
+      <c r="V1" s="61"/>
+      <c r="W1" s="61"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="61"/>
+      <c r="W2" s="61"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A3" s="58" t="s">
+      <c r="A3" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="57" t="s">
+      <c r="G3" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="61"/>
+      <c r="L3" s="61"/>
+      <c r="M3" s="61"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
-      <c r="Q3" s="57" t="s">
+      <c r="Q3" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="R3" s="57"/>
-      <c r="S3" s="57"/>
-      <c r="T3" s="57"/>
-      <c r="U3" s="57"/>
-      <c r="V3" s="57"/>
-      <c r="W3" s="57"/>
+      <c r="R3" s="61"/>
+      <c r="S3" s="61"/>
+      <c r="T3" s="61"/>
+      <c r="U3" s="61"/>
+      <c r="V3" s="61"/>
+      <c r="W3" s="61"/>
     </row>
     <row r="4" spans="1:23" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55" t="s">
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68" t="s">
         <v>85</v>
       </c>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55" t="s">
+      <c r="I4" s="68"/>
+      <c r="J4" s="68" t="s">
         <v>86</v>
       </c>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55" t="s">
+      <c r="K4" s="68"/>
+      <c r="L4" s="69" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4" s="69"/>
+      <c r="N4" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="O4" s="68"/>
+      <c r="P4" s="70" t="s">
         <v>87</v>
-      </c>
-      <c r="K4" s="55"/>
-      <c r="L4" s="56" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" s="56"/>
-      <c r="N4" s="55" t="s">
-        <v>36</v>
-      </c>
-      <c r="O4" s="55"/>
-      <c r="P4" s="70" t="s">
-        <v>88</v>
       </c>
       <c r="Q4" s="71"/>
       <c r="R4" s="72" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="S4" s="73"/>
       <c r="T4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="U4" s="56" t="s">
+      <c r="U4" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="V4" s="56"/>
-      <c r="W4" s="56" t="s">
+      <c r="V4" s="69"/>
+      <c r="W4" s="69" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A5" s="56"/>
-      <c r="B5" s="56"/>
+      <c r="A5" s="69"/>
+      <c r="B5" s="69"/>
       <c r="C5" s="11" t="s">
         <v>22</v>
       </c>
@@ -3570,11 +3565,11 @@
       <c r="V5" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W5" s="56"/>
+      <c r="W5" s="69"/>
     </row>
     <row r="6" spans="1:23" s="13" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="56"/>
-      <c r="B6" s="56"/>
+      <c r="A6" s="69"/>
+      <c r="B6" s="69"/>
       <c r="C6" s="12" t="s">
         <v>27</v>
       </c>
@@ -3640,45 +3635,45 @@
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="52"/>
-      <c r="K7" s="52"/>
-      <c r="L7" s="52"/>
-      <c r="M7" s="52"/>
-      <c r="N7" s="52"/>
-      <c r="O7" s="52"/>
-      <c r="P7" s="52"/>
-      <c r="Q7" s="52"/>
-      <c r="R7" s="52"/>
-      <c r="S7" s="52"/>
-      <c r="T7" s="52"/>
-      <c r="U7" s="52"/>
-      <c r="V7" s="52"/>
-      <c r="W7" s="52"/>
-    </row>
-    <row r="8" spans="1:23" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="64"/>
+      <c r="P7" s="64"/>
+      <c r="Q7" s="64"/>
+      <c r="R7" s="64"/>
+      <c r="S7" s="64"/>
+      <c r="T7" s="64"/>
+      <c r="U7" s="64"/>
+      <c r="V7" s="64"/>
+      <c r="W7" s="64"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
@@ -3686,15 +3681,15 @@
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
       <c r="M8" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N8" s="11"/>
       <c r="O8" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P8" s="11"/>
       <c r="Q8" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="R8" s="11"/>
       <c r="S8" s="11"/>
@@ -3703,23 +3698,23 @@
       <c r="V8" s="11"/>
       <c r="W8" s="11"/>
     </row>
-    <row r="9" spans="1:23" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
       <c r="I9" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
@@ -3729,7 +3724,7 @@
       <c r="O9" s="11"/>
       <c r="P9" s="11"/>
       <c r="Q9" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R9" s="11"/>
       <c r="S9" s="11"/>
@@ -3737,15 +3732,15 @@
       <c r="U9" s="11"/>
       <c r="V9" s="11"/>
       <c r="W9" s="11" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
@@ -3756,7 +3751,7 @@
       <c r="I10" s="11"/>
       <c r="J10" s="11"/>
       <c r="K10" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L10" s="11"/>
       <c r="M10" s="11"/>
@@ -3764,7 +3759,7 @@
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
       <c r="Q10" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R10" s="11"/>
       <c r="S10" s="11"/>
@@ -3773,12 +3768,12 @@
       <c r="V10" s="11"/>
       <c r="W10" s="11"/>
     </row>
-    <row r="11" spans="1:23" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -3795,7 +3790,7 @@
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
       <c r="Q11" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R11" s="11"/>
       <c r="S11" s="11"/>
@@ -3804,12 +3799,12 @@
       <c r="V11" s="11"/>
       <c r="W11" s="11"/>
     </row>
-    <row r="12" spans="1:23" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -3819,7 +3814,7 @@
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
       <c r="J12" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
@@ -3828,7 +3823,7 @@
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
       <c r="Q12" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R12" s="11"/>
       <c r="S12" s="11"/>
@@ -3837,12 +3832,12 @@
       <c r="V12" s="11"/>
       <c r="W12" s="11"/>
     </row>
-    <row r="13" spans="1:23" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -3859,7 +3854,7 @@
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
       <c r="Q13" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R13" s="11"/>
       <c r="S13" s="11"/>
@@ -3868,12 +3863,12 @@
       <c r="V13" s="11"/>
       <c r="W13" s="11"/>
     </row>
-    <row r="14" spans="1:23" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B14" s="29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -3888,11 +3883,11 @@
       <c r="M14" s="11"/>
       <c r="N14" s="11"/>
       <c r="O14" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P14" s="11"/>
       <c r="Q14" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R14" s="11"/>
       <c r="S14" s="11"/>
@@ -3901,12 +3896,12 @@
       <c r="V14" s="11"/>
       <c r="W14" s="11"/>
     </row>
-    <row r="15" spans="1:23" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="29" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -3926,13 +3921,13 @@
       <c r="R15" s="11"/>
       <c r="S15" s="11"/>
       <c r="T15" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U15" s="11"/>
       <c r="V15" s="11"/>
       <c r="W15" s="11"/>
     </row>
-    <row r="16" spans="1:23" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="11"/>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -3957,46 +3952,46 @@
       <c r="V16" s="11"/>
       <c r="W16" s="11"/>
     </row>
-    <row r="17" spans="1:23" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="53" t="s">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A17" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="54"/>
-      <c r="K17" s="54"/>
-      <c r="L17" s="54"/>
-      <c r="M17" s="54"/>
-      <c r="N17" s="54"/>
-      <c r="O17" s="54"/>
-      <c r="P17" s="54"/>
-      <c r="Q17" s="54"/>
-      <c r="R17" s="54"/>
-      <c r="S17" s="54"/>
-      <c r="T17" s="54"/>
-      <c r="U17" s="54"/>
-      <c r="V17" s="54"/>
-      <c r="W17" s="54"/>
-    </row>
-    <row r="18" spans="1:23" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="66"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="66"/>
+      <c r="G17" s="66"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="66"/>
+      <c r="J17" s="66"/>
+      <c r="K17" s="66"/>
+      <c r="L17" s="66"/>
+      <c r="M17" s="66"/>
+      <c r="N17" s="66"/>
+      <c r="O17" s="66"/>
+      <c r="P17" s="66"/>
+      <c r="Q17" s="66"/>
+      <c r="R17" s="66"/>
+      <c r="S17" s="66"/>
+      <c r="T17" s="66"/>
+      <c r="U17" s="66"/>
+      <c r="V17" s="66"/>
+      <c r="W17" s="66"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
       <c r="F18" s="15"/>
       <c r="G18" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H18" s="15"/>
       <c r="I18" s="15"/>
@@ -4015,12 +4010,12 @@
       <c r="V18" s="15"/>
       <c r="W18" s="15"/>
     </row>
-    <row r="19" spans="1:23" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
@@ -4033,7 +4028,7 @@
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
       <c r="M19" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N19" s="17"/>
       <c r="O19" s="17"/>
@@ -4046,12 +4041,12 @@
       <c r="V19" s="17"/>
       <c r="W19" s="17"/>
     </row>
-    <row r="20" spans="1:23" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -4074,20 +4069,20 @@
       <c r="U20" s="17"/>
       <c r="V20" s="17"/>
       <c r="W20" s="17" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
@@ -4108,12 +4103,12 @@
       <c r="V21" s="17"/>
       <c r="W21" s="17"/>
     </row>
-    <row r="22" spans="1:23" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
@@ -4127,7 +4122,7 @@
       <c r="L22" s="17"/>
       <c r="M22" s="17"/>
       <c r="N22" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O22" s="17"/>
       <c r="P22" s="17"/>
@@ -4139,12 +4134,12 @@
       <c r="V22" s="17"/>
       <c r="W22" s="17"/>
     </row>
-    <row r="23" spans="1:23" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
@@ -4158,7 +4153,7 @@
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O23" s="17"/>
       <c r="P23" s="17"/>
@@ -4170,12 +4165,12 @@
       <c r="V23" s="17"/>
       <c r="W23" s="17"/>
     </row>
-    <row r="24" spans="1:23" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C24" s="18"/>
       <c r="D24" s="17"/>
@@ -4197,16 +4192,16 @@
       <c r="T24" s="17"/>
       <c r="U24" s="17"/>
       <c r="V24" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W24" s="17"/>
     </row>
-    <row r="25" spans="1:23" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C25" s="19"/>
       <c r="D25" s="19"/>
@@ -4215,11 +4210,11 @@
       <c r="G25" s="15"/>
       <c r="H25" s="15"/>
       <c r="I25" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J25" s="15"/>
       <c r="K25" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
@@ -4232,16 +4227,16 @@
       <c r="T25" s="15"/>
       <c r="U25" s="15"/>
       <c r="V25" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="W25" s="15"/>
     </row>
-    <row r="26" spans="1:23" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C26" s="15"/>
       <c r="D26" s="19"/>
@@ -4261,18 +4256,18 @@
       <c r="R26" s="15"/>
       <c r="S26" s="15"/>
       <c r="T26" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U26" s="15"/>
       <c r="V26" s="15"/>
       <c r="W26" s="15"/>
     </row>
-    <row r="27" spans="1:23" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27" s="20" t="s">
         <v>110</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>111</v>
       </c>
       <c r="C27" s="17"/>
       <c r="D27" s="18"/>
@@ -4291,19 +4286,19 @@
       <c r="Q27" s="17"/>
       <c r="R27" s="17"/>
       <c r="S27" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T27" s="17"/>
       <c r="U27" s="15"/>
       <c r="V27" s="17"/>
       <c r="W27" s="17"/>
     </row>
-    <row r="28" spans="1:23" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="18"/>
@@ -4313,7 +4308,7 @@
       <c r="H28" s="17"/>
       <c r="I28" s="17"/>
       <c r="J28" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K28" s="17"/>
       <c r="L28" s="18"/>
@@ -4324,19 +4319,19 @@
       <c r="Q28" s="17"/>
       <c r="R28" s="17"/>
       <c r="S28" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T28" s="17"/>
       <c r="U28" s="15"/>
       <c r="V28" s="17"/>
       <c r="W28" s="17"/>
     </row>
-    <row r="29" spans="1:23" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C29" s="21"/>
       <c r="D29" s="22"/>
@@ -4355,14 +4350,14 @@
       <c r="Q29" s="21"/>
       <c r="R29" s="21"/>
       <c r="S29" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T29" s="21"/>
       <c r="U29" s="15"/>
       <c r="V29" s="21"/>
       <c r="W29" s="21"/>
     </row>
-    <row r="30" spans="1:23" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A30" s="14"/>
       <c r="B30" s="28" t="s">
         <v>32</v>
@@ -4390,29 +4385,29 @@
       <c r="W30" s="37"/>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A31" s="69"/>
-      <c r="B31" s="69"/>
-      <c r="C31" s="69"/>
-      <c r="D31" s="69"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="69"/>
-      <c r="H31" s="69"/>
-      <c r="I31" s="69"/>
-      <c r="J31" s="69"/>
-      <c r="K31" s="69"/>
-      <c r="L31" s="69"/>
-      <c r="M31" s="69"/>
-      <c r="N31" s="69"/>
-      <c r="O31" s="69"/>
-      <c r="P31" s="69"/>
-      <c r="Q31" s="69"/>
-      <c r="R31" s="69"/>
-      <c r="S31" s="69"/>
-      <c r="T31" s="69"/>
-      <c r="U31" s="69"/>
-      <c r="V31" s="69"/>
-      <c r="W31" s="69"/>
+      <c r="A31" s="67"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="67"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="67"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="67"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="67"/>
+      <c r="J31" s="67"/>
+      <c r="K31" s="67"/>
+      <c r="L31" s="67"/>
+      <c r="M31" s="67"/>
+      <c r="N31" s="67"/>
+      <c r="O31" s="67"/>
+      <c r="P31" s="67"/>
+      <c r="Q31" s="67"/>
+      <c r="R31" s="67"/>
+      <c r="S31" s="67"/>
+      <c r="T31" s="67"/>
+      <c r="U31" s="67"/>
+      <c r="V31" s="67"/>
+      <c r="W31" s="67"/>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
@@ -4427,16 +4422,11 @@
         <v>44</v>
       </c>
       <c r="W32" s="9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:W1"/>
-    <mergeCell ref="A2:W2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="G3:M3"/>
-    <mergeCell ref="Q3:W3"/>
     <mergeCell ref="A7:W7"/>
     <mergeCell ref="A17:W17"/>
     <mergeCell ref="A31:W31"/>
@@ -4452,6 +4442,11 @@
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="R4:S4"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A2:W2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="G3:M3"/>
+    <mergeCell ref="Q3:W3"/>
   </mergeCells>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape" r:id="rId1"/>
@@ -5983,134 +5978,134 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
-      <c r="S1" s="57"/>
-      <c r="T1" s="57"/>
-      <c r="U1" s="57"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="61"/>
+      <c r="P1" s="61"/>
+      <c r="Q1" s="61"/>
+      <c r="R1" s="61"/>
+      <c r="S1" s="61"/>
+      <c r="T1" s="61"/>
+      <c r="U1" s="61"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="58" t="s">
+      <c r="A3" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="57" t="s">
+      <c r="G3" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="61"/>
+      <c r="L3" s="61"/>
+      <c r="M3" s="61"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
-      <c r="Q3" s="57" t="s">
+      <c r="Q3" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="R3" s="57"/>
-      <c r="S3" s="57"/>
-      <c r="T3" s="57"/>
-      <c r="U3" s="57"/>
+      <c r="R3" s="61"/>
+      <c r="S3" s="61"/>
+      <c r="T3" s="61"/>
+      <c r="U3" s="61"/>
     </row>
     <row r="4" spans="1:21" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55" t="s">
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68" t="s">
         <v>116</v>
       </c>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55" t="s">
-        <v>117</v>
-      </c>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55" t="s">
+      <c r="I4" s="68"/>
+      <c r="J4" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="55"/>
-      <c r="L4" s="56" t="s">
+      <c r="K4" s="68"/>
+      <c r="L4" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="M4" s="56"/>
-      <c r="N4" s="56" t="s">
+      <c r="M4" s="69"/>
+      <c r="N4" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="O4" s="56"/>
-      <c r="P4" s="55" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q4" s="55"/>
+      <c r="O4" s="69"/>
+      <c r="P4" s="68" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q4" s="68"/>
       <c r="R4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="S4" s="56" t="s">
+      <c r="S4" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="T4" s="56"/>
-      <c r="U4" s="56" t="s">
+      <c r="T4" s="69"/>
+      <c r="U4" s="69" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A5" s="56"/>
-      <c r="B5" s="56"/>
+      <c r="A5" s="69"/>
+      <c r="B5" s="69"/>
       <c r="C5" s="11" t="s">
         <v>22</v>
       </c>
@@ -6165,11 +6160,11 @@
       <c r="T5" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="U5" s="56"/>
+      <c r="U5" s="69"/>
     </row>
     <row r="6" spans="1:21" s="13" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="56"/>
-      <c r="B6" s="56"/>
+      <c r="A6" s="69"/>
+      <c r="B6" s="69"/>
       <c r="C6" s="12" t="s">
         <v>27</v>
       </c>
@@ -6229,43 +6224,43 @@
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="52"/>
-      <c r="K7" s="52"/>
-      <c r="L7" s="52"/>
-      <c r="M7" s="52"/>
-      <c r="N7" s="52"/>
-      <c r="O7" s="52"/>
-      <c r="P7" s="52"/>
-      <c r="Q7" s="52"/>
-      <c r="R7" s="52"/>
-      <c r="S7" s="52"/>
-      <c r="T7" s="52"/>
-      <c r="U7" s="52"/>
-    </row>
-    <row r="8" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="64"/>
+      <c r="P7" s="64"/>
+      <c r="Q7" s="64"/>
+      <c r="R7" s="64"/>
+      <c r="S7" s="64"/>
+      <c r="T7" s="64"/>
+      <c r="U7" s="64"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
@@ -6277,19 +6272,19 @@
       <c r="O8" s="11"/>
       <c r="P8" s="11"/>
       <c r="Q8" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R8" s="11"/>
       <c r="S8" s="11"/>
       <c r="T8" s="11"/>
       <c r="U8" s="11"/>
     </row>
-    <row r="9" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
@@ -6310,26 +6305,26 @@
       <c r="S9" s="11"/>
       <c r="T9" s="11"/>
       <c r="U9" s="11" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
@@ -6343,15 +6338,15 @@
       <c r="S10" s="11"/>
       <c r="T10" s="11"/>
       <c r="U10" s="11" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -6368,19 +6363,19 @@
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
       <c r="Q11" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R11" s="11"/>
       <c r="S11" s="11"/>
       <c r="T11" s="11"/>
       <c r="U11" s="11"/>
     </row>
-    <row r="12" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -6388,9 +6383,6 @@
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
-      <c r="I12" s="11" t="s">
-        <v>93</v>
-      </c>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
@@ -6398,18 +6390,20 @@
       <c r="N12" s="11"/>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
+      <c r="Q12" s="11" t="s">
+        <v>92</v>
+      </c>
       <c r="R12" s="11"/>
       <c r="S12" s="11"/>
       <c r="T12" s="11"/>
       <c r="U12" s="11"/>
     </row>
-    <row r="13" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -6417,9 +6411,6 @@
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
       <c r="H13" s="11"/>
-      <c r="I13" s="11" t="s">
-        <v>94</v>
-      </c>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
@@ -6427,18 +6418,20 @@
       <c r="N13" s="11"/>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
+      <c r="Q13" s="11" t="s">
+        <v>93</v>
+      </c>
       <c r="R13" s="11"/>
       <c r="S13" s="11"/>
       <c r="T13" s="11"/>
       <c r="U13" s="11"/>
     </row>
-    <row r="14" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B14" s="29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -6447,7 +6440,7 @@
       <c r="G14" s="11"/>
       <c r="H14" s="11"/>
       <c r="I14" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
@@ -6462,7 +6455,7 @@
       <c r="T14" s="11"/>
       <c r="U14" s="11"/>
     </row>
-    <row r="15" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="11"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -6485,44 +6478,44 @@
       <c r="T15" s="11"/>
       <c r="U15" s="11"/>
     </row>
-    <row r="16" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="53" t="s">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="54"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="54"/>
-      <c r="K16" s="54"/>
-      <c r="L16" s="54"/>
-      <c r="M16" s="54"/>
-      <c r="N16" s="54"/>
-      <c r="O16" s="54"/>
-      <c r="P16" s="54"/>
-      <c r="Q16" s="54"/>
-      <c r="R16" s="54"/>
-      <c r="S16" s="54"/>
-      <c r="T16" s="54"/>
-      <c r="U16" s="54"/>
-    </row>
-    <row r="17" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="66"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="66"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="66"/>
+      <c r="G16" s="66"/>
+      <c r="H16" s="66"/>
+      <c r="I16" s="66"/>
+      <c r="J16" s="66"/>
+      <c r="K16" s="66"/>
+      <c r="L16" s="66"/>
+      <c r="M16" s="66"/>
+      <c r="N16" s="66"/>
+      <c r="O16" s="66"/>
+      <c r="P16" s="66"/>
+      <c r="Q16" s="66"/>
+      <c r="R16" s="66"/>
+      <c r="S16" s="66"/>
+      <c r="T16" s="66"/>
+      <c r="U16" s="66"/>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
       <c r="F17" s="15"/>
       <c r="G17" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H17" s="15"/>
       <c r="I17" s="15"/>
@@ -6539,17 +6532,17 @@
       <c r="T17" s="15"/>
       <c r="U17" s="15"/>
     </row>
-    <row r="18" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
@@ -6568,12 +6561,12 @@
       <c r="T18" s="17"/>
       <c r="U18" s="17"/>
     </row>
-    <row r="19" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
@@ -6588,7 +6581,7 @@
       <c r="M19" s="43"/>
       <c r="N19" s="17"/>
       <c r="O19" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P19" s="17"/>
       <c r="Q19" s="17"/>
@@ -6597,12 +6590,12 @@
       <c r="T19" s="17"/>
       <c r="U19" s="17"/>
     </row>
-    <row r="20" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" s="16" t="s">
         <v>110</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>111</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -6617,7 +6610,7 @@
       <c r="M20" s="43"/>
       <c r="N20" s="17"/>
       <c r="O20" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P20" s="17"/>
       <c r="Q20" s="17"/>
@@ -6626,7 +6619,7 @@
       <c r="T20" s="17"/>
       <c r="U20" s="17"/>
     </row>
-    <row r="21" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A21" s="14"/>
       <c r="B21" s="28" t="s">
         <v>32</v>
@@ -6651,7 +6644,7 @@
       <c r="T21" s="37"/>
       <c r="U21" s="37"/>
     </row>
-    <row r="22" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="30"/>
       <c r="B22" s="31"/>
       <c r="C22" s="32"/>
@@ -6674,7 +6667,7 @@
       <c r="T22" s="32"/>
       <c r="U22" s="32"/>
     </row>
-    <row r="23" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="25" t="s">
         <v>31</v>
       </c>
@@ -6685,16 +6678,11 @@
         <v>44</v>
       </c>
       <c r="U23" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:U2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="G3:M3"/>
-    <mergeCell ref="Q3:U3"/>
     <mergeCell ref="A7:U7"/>
     <mergeCell ref="A16:U16"/>
     <mergeCell ref="J4:K4"/>
@@ -6708,6 +6696,11 @@
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:I4"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="G3:M3"/>
+    <mergeCell ref="Q3:U3"/>
   </mergeCells>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape" r:id="rId1"/>
